--- a/public/ssg_templates/Enrolment_Upload_Template.xlsx
+++ b/public/ssg_templates/Enrolment_Upload_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B68B6DC-3E29-490F-B766-3F181DB2E9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E00316F-08C8-4F29-8A56-9902A8EA1282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="0" windowWidth="16080" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1356" yWindow="1128" windowWidth="14232" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enrolment Upload Template" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
   <si>
     <t>Description</t>
   </si>
@@ -295,6 +295,9 @@
   <si>
     <t>Bundle code for which trainee is being enrolled.
 Ensure that SSG-BC-0000-000001 is indicated for non-SCTP trainees.</t>
+  </si>
+  <si>
+    <t>Course Reference Code*</t>
   </si>
 </sst>
 </file>
@@ -789,31 +792,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="2" width="15.21875" customWidth="1"/>
     <col min="3" max="3" width="22.5546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="24" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.5546875" customWidth="1"/>
-    <col min="12" max="12" width="33" customWidth="1"/>
-    <col min="13" max="13" width="26.44140625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="35.5546875" customWidth="1"/>
-    <col min="15" max="15" width="33.77734375" customWidth="1"/>
-    <col min="16" max="16" width="32.5546875" customWidth="1"/>
-    <col min="17" max="17" width="33.44140625" style="7" customWidth="1"/>
-    <col min="18" max="18" width="22.44140625" style="8" customWidth="1"/>
-    <col min="19" max="19" width="29.5546875" customWidth="1"/>
+    <col min="4" max="5" width="24" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.21875" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="25.5546875" customWidth="1"/>
+    <col min="13" max="13" width="33" customWidth="1"/>
+    <col min="14" max="14" width="26.44140625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="35.5546875" customWidth="1"/>
+    <col min="16" max="16" width="33.77734375" customWidth="1"/>
+    <col min="17" max="17" width="32.5546875" customWidth="1"/>
+    <col min="18" max="18" width="33.44140625" style="7" customWidth="1"/>
+    <col min="19" max="19" width="22.44140625" style="8" customWidth="1"/>
+    <col min="20" max="20" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -827,77 +830,84 @@
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B2" s="17"/>
       <c r="C2" s="19"/>
-      <c r="F2" s="16"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" s="17"/>
       <c r="C3" s="18"/>
       <c r="D3" s="17"/>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="E3" s="17"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C4" s="18"/>
       <c r="D4" s="17"/>
-      <c r="F4" s="16"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="E4" s="17"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B5" s="17"/>
       <c r="C5" s="19"/>
       <c r="D5" s="17"/>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="E5" s="17"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C6" s="19"/>
       <c r="D6" s="17"/>
-      <c r="F6" s="16"/>
+      <c r="E6" s="17"/>
+      <c r="G6" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -906,11 +916,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{AA028633-A981-4F73-952F-79CDD657F3CD}">
       <formula1>"NRIC, FIN, Others"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{470B571B-9697-4247-987D-B39948918885}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576" xr:uid="{470B571B-9697-4247-987D-B39948918885}">
       <formula1>"Individual, Employer"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Date should be in DD-MM-YYYY format" sqref="C7:C1048576" xr:uid="{B4C8857C-2509-4FF0-AF6C-0E31081DFB6A}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576" xr:uid="{88F9DACE-1AC7-4B4B-9A7E-665717D76F66}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{88F9DACE-1AC7-4B4B-9A7E-665717D76F66}">
       <formula1>"Pending Payment, Partial Payment, Full Payment"</formula1>
     </dataValidation>
   </dataValidations>
